--- a/docs/olife-geo/장소_질문_2차.xlsx
+++ b/docs/olife-geo/장소_질문_2차.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="121">
   <si>
     <t>프로그램</t>
   </si>
@@ -37,298 +37,343 @@
     <t>세부 장소 (답, 쉼표로 여러 곳)</t>
   </si>
   <si>
+    <t>걸세</t>
+  </si>
+  <si>
+    <t>스위스 알프스 - 만년설이 유혹하다</t>
+  </si>
+  <si>
+    <t>스위스</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>스와질란드 - 아프리카의 스위스</t>
+  </si>
+  <si>
+    <t>에스와티니</t>
+  </si>
+  <si>
     <t>세테기</t>
   </si>
   <si>
-    <t>중국한시기행9 황허(黃河)2 3-4부</t>
+    <t>그 여름의 끝, 그리스 섬 기행 4부</t>
+  </si>
+  <si>
+    <t>그리스</t>
+  </si>
+  <si>
+    <t>차이 나는 중국 기행 3-4부</t>
   </si>
   <si>
     <t>중국</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>상상보다 멋진 튀르키예 3부</t>
+    <t>알프스 따라 스위스 1-2부</t>
+  </si>
+  <si>
+    <t>실크로드 재발견 튀르키예 1-2부</t>
   </si>
   <si>
     <t>튀르키예</t>
   </si>
   <si>
-    <t>중국고사유랑1 3부</t>
-  </si>
-  <si>
-    <t>상상보다 멋진 튀르키예 1-2부</t>
-  </si>
-  <si>
-    <t>상상보다 멋진 튀르키예 3-4부</t>
-  </si>
-  <si>
-    <t>걸세</t>
-  </si>
-  <si>
-    <t>탄자니아 - 인도양에서 아프리카의 지붕까지</t>
-  </si>
-  <si>
-    <t>탄자니아</t>
-  </si>
-  <si>
-    <t>황금보다 아름다운 골든 트라이앵글 1-2부</t>
+    <t>그 여름의 끝, 그리스 섬 기행 3부</t>
+  </si>
+  <si>
+    <t>태평양의 행복한 메아리 - 마셜제도</t>
+  </si>
+  <si>
+    <t>북한</t>
+  </si>
+  <si>
+    <t>정다운 아시아 4부-신비한 필리핀</t>
+  </si>
+  <si>
+    <t>필리핀</t>
+  </si>
+  <si>
+    <t>멕시코 칸쿤 - 카브리해 천국의 문</t>
+  </si>
+  <si>
+    <t>멕시코</t>
+  </si>
+  <si>
+    <t>히말라야의 동물들 네팔에 반하다 3-4부</t>
+  </si>
+  <si>
+    <t>네팔</t>
+  </si>
+  <si>
+    <t>파키스탄 - 향기로운 땅</t>
+  </si>
+  <si>
+    <t>파키스탄</t>
+  </si>
+  <si>
+    <t>알프스 따라 스위스 3-4부</t>
+  </si>
+  <si>
+    <t>정다운 아시아 1부 -행복한 부탄</t>
+  </si>
+  <si>
+    <t>부탄</t>
+  </si>
+  <si>
+    <t>영국 - 영국의 정원, 켄트</t>
+  </si>
+  <si>
+    <t>영국</t>
+  </si>
+  <si>
+    <t>동유럽 리버크루즈), 397(라트비아-수줍은 미소의 나라</t>
+  </si>
+  <si>
+    <t>라트비아</t>
+  </si>
+  <si>
+    <t>일본 - 가을 향기 속 설렘을 찾아</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>UHD특집 1부 - 아이슬란드</t>
+  </si>
+  <si>
+    <t>아이슬란드</t>
+  </si>
+  <si>
+    <t>방글라데시 - 소박한 꿈과 미소의 나라</t>
+  </si>
+  <si>
+    <t>방글라데시</t>
+  </si>
+  <si>
+    <t>황금빛 도시에서 순수를 만나다 - 미얀마</t>
+  </si>
+  <si>
+    <t>미얀마</t>
+  </si>
+  <si>
+    <t>로맨틱 홀리데이, 체코 1-2부</t>
+  </si>
+  <si>
+    <t>체코</t>
+  </si>
+  <si>
+    <t>인도 - 언덕의 여왕, 만년설이 유혹하다</t>
+  </si>
+  <si>
+    <t>인도</t>
+  </si>
+  <si>
+    <t>내 인생의 피에스타 콜롬비아 4부</t>
+  </si>
+  <si>
+    <t>콜롬비아</t>
+  </si>
+  <si>
+    <t>마음이 평화로운 나라 - 브루나이</t>
+  </si>
+  <si>
+    <t>브루나이</t>
+  </si>
+  <si>
+    <t>싱가포르 - 도시를 걷다</t>
+  </si>
+  <si>
+    <t>싱가포르</t>
+  </si>
+  <si>
+    <t>일본 - 규슈 올레를 걷다</t>
+  </si>
+  <si>
+    <t>불가리아 - 산, 장비, 수도원 그리고 불가리아</t>
+  </si>
+  <si>
+    <t>불가리아</t>
+  </si>
+  <si>
+    <t>그 섬에 가면 인도네시아 1-2부</t>
+  </si>
+  <si>
+    <t>인도네시아</t>
+  </si>
+  <si>
+    <t>한번쯤은, 하염없이 몽골 1-3부</t>
+  </si>
+  <si>
+    <t>몽골</t>
+  </si>
+  <si>
+    <t>그리스 로도스 - 태양과 함께 빛나다</t>
+  </si>
+  <si>
+    <t>정다운 아시아 3부-궁금한 라오스</t>
+  </si>
+  <si>
+    <t>라오스</t>
+  </si>
+  <si>
+    <t>알수록 놀라운, 베트남 남부 3-4부</t>
+  </si>
+  <si>
+    <t>베트남</t>
+  </si>
+  <si>
+    <t>페루 푸노 - 하늘길을 걷다</t>
+  </si>
+  <si>
+    <t>페루</t>
+  </si>
+  <si>
+    <t>인도 - 다채로운 빛깔의 여유</t>
+  </si>
+  <si>
+    <t>미국 - 미국 서부의 품격, 센트럴 코스트</t>
+  </si>
+  <si>
+    <t>미국</t>
+  </si>
+  <si>
+    <t>중국 명산 기행 3-4부</t>
+  </si>
+  <si>
+    <t>모로코 - 문화의 용광로</t>
+  </si>
+  <si>
+    <t>모로코</t>
+  </si>
+  <si>
+    <t>남미의 심장 - 파라과이</t>
+  </si>
+  <si>
+    <t>파라과이</t>
+  </si>
+  <si>
+    <t>내 인생의 피에스타 콜롬비아 2부</t>
+  </si>
+  <si>
+    <t>중국한시기행4-한시와 떠나는 실크로드 1-2부</t>
+  </si>
+  <si>
+    <t>대서양에 부는 뜨거운 바람 - 브라질</t>
+  </si>
+  <si>
+    <t>브라질</t>
+  </si>
+  <si>
+    <t>내 인생의 피에스타 콜롬비아 3부</t>
+  </si>
+  <si>
+    <t>캐나다 - 캐나다의 새로운 느낌, 유콘</t>
+  </si>
+  <si>
+    <t>캐나다</t>
+  </si>
+  <si>
+    <t>조지아 - 기어이 지켜낸 땅</t>
+  </si>
+  <si>
+    <t>조지아</t>
+  </si>
+  <si>
+    <t>도미니카-카리브 해의 중심, 도미니카), 465(모로코-문화의 용광로</t>
+  </si>
+  <si>
+    <t>아르헨티나 파타고니아 - 바람이 품은 아름다움</t>
+  </si>
+  <si>
+    <t>아르헨티나</t>
+  </si>
+  <si>
+    <t>중국 - 삶은 노래가 되고</t>
+  </si>
+  <si>
+    <t>콜롬비아 메데인 - 인데스의 두 얼굴</t>
+  </si>
+  <si>
+    <t>중국 남부 핫 플레이스 1-2부</t>
+  </si>
+  <si>
+    <t>정다운 아시아 2부-캄보디아</t>
+  </si>
+  <si>
+    <t>캄보디아</t>
+  </si>
+  <si>
+    <t>아일랜드 - 문학과 열정의 나라</t>
+  </si>
+  <si>
+    <t>아일랜드</t>
+  </si>
+  <si>
+    <t>이집트 - 파라오의 땅, 신화를 만나다</t>
+  </si>
+  <si>
+    <t>이집트</t>
+  </si>
+  <si>
+    <t>자연이 그리워서,동말레이시아 3-4부</t>
+  </si>
+  <si>
+    <t>말레이시아</t>
+  </si>
+  <si>
+    <t>짐바브웨 - 위대한 야생의 나라</t>
+  </si>
+  <si>
+    <t>짐바브웨</t>
+  </si>
+  <si>
+    <t>보고 싶었다,크로아티아 1-2부</t>
+  </si>
+  <si>
+    <t>크로아티아</t>
+  </si>
+  <si>
+    <t>베트남 육향만리 3-4부</t>
+  </si>
+  <si>
+    <t>미국 서부</t>
+  </si>
+  <si>
+    <t>인도네시아 - 고대 문명의 나라, 인도네시아</t>
+  </si>
+  <si>
+    <t>열정이 그리워서, 스페인 1-2부</t>
+  </si>
+  <si>
+    <t>스페인</t>
+  </si>
+  <si>
+    <t>태국 끄라비, 뜨랑 - 신비와 모험의 땅</t>
   </si>
   <si>
     <t>태국</t>
   </si>
   <si>
-    <t>중국한시기행9 황허(黃河)2 1-2부</t>
-  </si>
-  <si>
-    <t>러시아 - 러시아의 붉은 심장</t>
+    <t>러시아 블라디보스토크 - 아시아의 러시아</t>
   </si>
   <si>
     <t>러시아</t>
   </si>
   <si>
-    <t>베트남 중부 - 따스한 미소가 꽃피다</t>
-  </si>
-  <si>
-    <t>베트남</t>
-  </si>
-  <si>
-    <t>중국 소수민족 음식 기행 1-2부</t>
-  </si>
-  <si>
-    <t>황금보다 아름다운 골든 트라이앵글 3-4부</t>
-  </si>
-  <si>
-    <t>중국고사유랑1 3-4부</t>
-  </si>
-  <si>
-    <t>히말라야의 동물들 네팔에 반하다 1-2부</t>
-  </si>
-  <si>
-    <t>네팔</t>
-  </si>
-  <si>
-    <t>노르웨이 - 빙하가 빚은 대자연, 노르웨이 서부</t>
-  </si>
-  <si>
-    <t>노르웨이</t>
-  </si>
-  <si>
-    <t>남아공 - 지구의 끝</t>
-  </si>
-  <si>
-    <t>남아프리카공화국</t>
-  </si>
-  <si>
-    <t>중국고사유랑1 1-2부</t>
-  </si>
-  <si>
-    <t>네팔 - 열대림을 품은 히말라야의 나라</t>
-  </si>
-  <si>
-    <t>자연에 묻힌 앙코르의 전설 - 캄보디아 씨엠립</t>
-  </si>
-  <si>
-    <t>캄보디아</t>
-  </si>
-  <si>
-    <t>과테말라 - 마야의 중심</t>
-  </si>
-  <si>
-    <t>과테말라</t>
-  </si>
-  <si>
-    <t>아프리카 버킷리스트,탄자니아 3-4부</t>
-  </si>
-  <si>
-    <t>실크로드 재발견 튀르키예 3-4부</t>
-  </si>
-  <si>
-    <t>천국 위에 태국 3-4부</t>
-  </si>
-  <si>
-    <t>중국 소수민족 음식 기행 4부</t>
-  </si>
-  <si>
-    <t>지치고 힘들 때 노르웨이 3-4부</t>
-  </si>
-  <si>
-    <t>지치고 힘들 때 노르웨이 1-2부</t>
-  </si>
-  <si>
-    <t>기다렸다, 그 맛! 타이완 3-4부</t>
-  </si>
-  <si>
-    <t>타이완</t>
-  </si>
-  <si>
-    <t>한번쯤은, 하염없이 몽골 1-3부</t>
-  </si>
-  <si>
-    <t>몽골</t>
-  </si>
-  <si>
-    <t>중국 소수민족 음식 기행 3부</t>
-  </si>
-  <si>
-    <t>미얀마 - 미얀마 기차여행</t>
-  </si>
-  <si>
-    <t>미얀마</t>
-  </si>
-  <si>
-    <t>그 섬에 가면 인도네시아 3-4부</t>
-  </si>
-  <si>
-    <t>인도네시아</t>
-  </si>
-  <si>
-    <t>아랍에미리트 아부다비 - 중동의 문화수도를 꿈꾼다</t>
-  </si>
-  <si>
-    <t>아랍에미리트</t>
-  </si>
-  <si>
-    <t>하늘이 주는 선물 오로라, 캐나다</t>
-  </si>
-  <si>
-    <t>캐나다</t>
-  </si>
-  <si>
-    <t>태양과 가장 가까운 곳, 적도의 안데스 - 에콰도르</t>
-  </si>
-  <si>
-    <t>에콰도르</t>
-  </si>
-  <si>
-    <t>신이 만든 놀이터, 노르웨이 3-4부</t>
-  </si>
-  <si>
-    <t>라트비아 - 수줍은 미소의 나라</t>
-  </si>
-  <si>
-    <t>라트비아</t>
-  </si>
-  <si>
-    <t>천국 위에 태국 1-2부</t>
-  </si>
-  <si>
-    <t>몰도바 - 작지만 강한 나라, 몰도바</t>
-  </si>
-  <si>
-    <t>몰도바</t>
-  </si>
-  <si>
-    <t>이탈리아 알토 아디제 - 티롤 왕국을 찾아서</t>
-  </si>
-  <si>
-    <t>이탈리아, 오스트리아</t>
-  </si>
-  <si>
-    <t>그 여름의 끝, 그리스 섬 기행 1부</t>
-  </si>
-  <si>
-    <t>그리스</t>
-  </si>
-  <si>
-    <t>풍요의 아프리카, 나미비아</t>
-  </si>
-  <si>
-    <t>나미비아</t>
-  </si>
-  <si>
-    <t>그 여름의 끝, 그리스 섬 기행 2부</t>
-  </si>
-  <si>
-    <t>스웨덴 - 스웨덴의 가을 속으로</t>
-  </si>
-  <si>
-    <t>스웨덴</t>
-  </si>
-  <si>
-    <t>기다렸다, 그 맛! 타이완 1-2부</t>
-  </si>
-  <si>
-    <t>뉴질랜드 남섬 - 순수 자연이 유혹하다</t>
-  </si>
-  <si>
-    <t>뉴질랜드</t>
-  </si>
-  <si>
-    <t>베트남 하이퐁 - 왕이 사랑한 바다</t>
-  </si>
-  <si>
-    <t>미지의 섬나라 - 마다가스카르), 396(불가리아-산, 장비, 수도원 그리고 불가리아</t>
-  </si>
-  <si>
-    <t>불가리아</t>
-  </si>
-  <si>
-    <t>벨기에 - 모자이크로 멋진 화음을</t>
-  </si>
-  <si>
-    <t>벨기에</t>
-  </si>
-  <si>
-    <t>구름이 빚은 무지개 나라 - 겨울 아일랜드</t>
-  </si>
-  <si>
-    <t>아일랜드</t>
-  </si>
-  <si>
-    <t>코스타리카 - 화산, 커피 그리고 뿌라비다</t>
-  </si>
-  <si>
-    <t>코스타리카</t>
-  </si>
-  <si>
-    <t>키르기스스탄 - 중앙아시아의 후른 섬</t>
-  </si>
-  <si>
-    <t>키르기스스탄</t>
-  </si>
-  <si>
-    <t>중국 - 지린성, 겨울왕국을 가다</t>
-  </si>
-  <si>
-    <t>포르투갈 - 어제의 바다를 걷다</t>
-  </si>
-  <si>
-    <t>포르투갈</t>
-  </si>
-  <si>
-    <t>동양의 에메랄드 - 말레이시아 페낭</t>
-  </si>
-  <si>
-    <t>말레이시아</t>
-  </si>
-  <si>
-    <t>잉글랜드의 녹색 심장 - 요크셔·레이크 디스크릭트</t>
-  </si>
-  <si>
-    <t>영국</t>
-  </si>
-  <si>
-    <t>멕시코 유카탄 - 삶은 계속된다</t>
-  </si>
-  <si>
-    <t>멕시코</t>
-  </si>
-  <si>
-    <t>우간다 - 원색의 자연 속으로</t>
-  </si>
-  <si>
-    <t>우간다</t>
-  </si>
-  <si>
-    <t>아프리카 버킷리스트,탄자니아 1-2부</t>
-  </si>
-  <si>
-    <t>칠레에서 세계 일주 3-4부</t>
-  </si>
-  <si>
-    <t>칠레</t>
+    <t>차이 나는 중국 기행 1-2부</t>
+  </si>
+  <si>
+    <t>남태평양 사모아</t>
+  </si>
+  <si>
+    <t>스페인 안달루시아 - 이슬람 문명의 흔적</t>
+  </si>
+  <si>
+    <t>베트남 육향만리 1-2부</t>
+  </si>
+  <si>
+    <t>아르헨티나 - 전설 속 행운을 만나다</t>
   </si>
 </sst>
 </file>
@@ -751,7 +796,7 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>2093</v>
+        <v>407</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -760,10 +805,10 @@
         <v>10</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0.175</v>
+        <v>0.139</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -777,7 +822,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>2028</v>
+        <v>372</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -786,10 +831,10 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>0.142</v>
+        <v>0.116</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -800,22 +845,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B4">
-        <v>3298</v>
+        <v>2113</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
         <v>10</v>
       </c>
-      <c r="E4">
-        <v>19</v>
-      </c>
       <c r="F4">
-        <v>0.117</v>
+        <v>0.139</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -826,22 +871,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>2027</v>
+        <v>2959</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>0.13</v>
+        <v>0.154</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -852,22 +897,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B6">
-        <v>2029</v>
+        <v>3260</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>0.147</v>
+        <v>0.138</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -878,22 +923,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B7">
-        <v>404</v>
+        <v>3261</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>0.167</v>
+        <v>0.138</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -904,22 +949,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>2026</v>
+        <v>3293</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -930,22 +975,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B9">
-        <v>2075</v>
+        <v>2112</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>0.132</v>
+        <v>0.137</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
@@ -959,19 +1004,19 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>2091</v>
+        <v>332</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F10">
-        <v>0.161</v>
+        <v>0.124</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -982,22 +1027,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>446</v>
+        <v>2984</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>0.161</v>
+        <v>0.151</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -1008,22 +1053,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B12">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F12">
-        <v>0.139</v>
+        <v>0.123</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -1034,22 +1079,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>2058</v>
+        <v>2024</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>0.149</v>
+        <v>0.113</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -1060,22 +1105,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B14">
-        <v>2059</v>
+        <v>2025</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F14">
-        <v>0.148</v>
+        <v>0.113</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -1089,19 +1134,19 @@
         <v>8</v>
       </c>
       <c r="B15">
-        <v>2074</v>
+        <v>526</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E15">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F15">
-        <v>0.129</v>
+        <v>0.169</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -1112,22 +1157,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>2077</v>
+        <v>3262</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>0.136</v>
+        <v>0.147</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1138,22 +1183,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B17">
-        <v>2076</v>
+        <v>3292</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
         <v>21</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F17">
-        <v>0.136</v>
+        <v>0.12</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -1164,22 +1209,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B18">
-        <v>2092</v>
+        <v>2981</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18">
         <v>10</v>
       </c>
-      <c r="E18">
-        <v>13</v>
-      </c>
       <c r="F18">
-        <v>0.156</v>
+        <v>0.132</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -1193,19 +1238,19 @@
         <v>8</v>
       </c>
       <c r="B19">
-        <v>3299</v>
+        <v>414</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E19">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>0.119</v>
+        <v>0.146</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -1219,19 +1264,19 @@
         <v>8</v>
       </c>
       <c r="B20">
-        <v>2090</v>
+        <v>532</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F20">
-        <v>0.155</v>
+        <v>0.119</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
@@ -1245,19 +1290,19 @@
         <v>8</v>
       </c>
       <c r="B21">
-        <v>2023</v>
+        <v>410</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
@@ -1271,19 +1316,19 @@
         <v>8</v>
       </c>
       <c r="B22">
-        <v>2022</v>
+        <v>531</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E22">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F22">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="G22" t="s">
         <v>11</v>
@@ -1294,22 +1339,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B23">
-        <v>455</v>
+        <v>522</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E23">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F23">
-        <v>0.173</v>
+        <v>0.13</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
@@ -1320,22 +1365,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B24">
-        <v>380</v>
+        <v>302</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="E24">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F24">
-        <v>0.145</v>
+        <v>0.118</v>
       </c>
       <c r="G24" t="s">
         <v>11</v>
@@ -1346,22 +1391,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B25">
-        <v>3296</v>
+        <v>2958</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E25">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>0.099</v>
+        <v>0.144</v>
       </c>
       <c r="G25" t="s">
         <v>11</v>
@@ -1372,22 +1417,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B26">
-        <v>379</v>
+        <v>3156</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F26">
-        <v>0.124</v>
+        <v>0.117</v>
       </c>
       <c r="G26" t="s">
         <v>11</v>
@@ -1398,22 +1443,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B27">
-        <v>3297</v>
+        <v>3157</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="E27">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F27">
-        <v>0.102</v>
+        <v>0.117</v>
       </c>
       <c r="G27" t="s">
         <v>11</v>
@@ -1424,22 +1469,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B28">
-        <v>284</v>
+        <v>413</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E28">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F28">
-        <v>0.14</v>
+        <v>0.126</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
@@ -1450,22 +1495,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B29">
-        <v>367</v>
+        <v>3191</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F29">
-        <v>0.12</v>
+        <v>0.126</v>
       </c>
       <c r="G29" t="s">
         <v>11</v>
@@ -1479,19 +1524,19 @@
         <v>8</v>
       </c>
       <c r="B30">
-        <v>3147</v>
+        <v>358</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F30">
-        <v>0.148</v>
+        <v>0.114</v>
       </c>
       <c r="G30" t="s">
         <v>11</v>
@@ -1505,19 +1550,19 @@
         <v>8</v>
       </c>
       <c r="B31">
-        <v>3295</v>
+        <v>394</v>
       </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>0.161</v>
+        <v>0.104</v>
       </c>
       <c r="G31" t="s">
         <v>11</v>
@@ -1531,19 +1576,19 @@
         <v>8</v>
       </c>
       <c r="B32">
-        <v>3275</v>
+        <v>459</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E32">
         <v>10</v>
       </c>
       <c r="F32">
-        <v>0.177</v>
+        <v>0.124</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
@@ -1557,19 +1602,19 @@
         <v>8</v>
       </c>
       <c r="B33">
-        <v>2061</v>
+        <v>396</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D33" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E33">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F33">
-        <v>0.135</v>
+        <v>0.113</v>
       </c>
       <c r="G33" t="s">
         <v>11</v>
@@ -1580,22 +1625,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B34">
-        <v>3146</v>
+        <v>2062</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F34">
-        <v>0.144</v>
+        <v>0.095</v>
       </c>
       <c r="G34" t="s">
         <v>11</v>
@@ -1606,22 +1651,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B35">
-        <v>2069</v>
+        <v>2390</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="E35">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F35">
-        <v>0.132</v>
+        <v>0.112</v>
       </c>
       <c r="G35" t="s">
         <v>11</v>
@@ -1635,19 +1680,19 @@
         <v>8</v>
       </c>
       <c r="B36">
-        <v>2067</v>
+        <v>419</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E36">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F36">
-        <v>0.131</v>
+        <v>0.103</v>
       </c>
       <c r="G36" t="s">
         <v>11</v>
@@ -1658,19 +1703,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B37">
-        <v>3178</v>
+        <v>2983</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="E37">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F37">
         <v>0.154</v>
@@ -1684,22 +1729,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B38">
-        <v>2388</v>
+        <v>3151</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D38" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="E38">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F38">
-        <v>0.13</v>
+        <v>0.122</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -1710,22 +1755,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B39">
-        <v>2389</v>
+        <v>3263</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E39">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F39">
-        <v>0.13</v>
+        <v>0.135</v>
       </c>
       <c r="G39" t="s">
         <v>11</v>
@@ -1739,19 +1784,19 @@
         <v>8</v>
       </c>
       <c r="B40">
-        <v>2060</v>
+        <v>425</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D40" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="E40">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F40">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -1762,22 +1807,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B41">
-        <v>484</v>
+        <v>370</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E41">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F41">
-        <v>0.168</v>
+        <v>0.109</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -1791,19 +1836,19 @@
         <v>8</v>
       </c>
       <c r="B42">
-        <v>2065</v>
+        <v>470</v>
       </c>
       <c r="C42" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E42">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F42">
-        <v>0.128</v>
+        <v>0.109</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -1814,22 +1859,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B43">
-        <v>421</v>
+        <v>3150</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E43">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F43">
-        <v>0.151</v>
+        <v>0.119</v>
       </c>
       <c r="G43" t="s">
         <v>11</v>
@@ -1840,22 +1885,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B44">
-        <v>3274</v>
+        <v>3632</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E44">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F44">
-        <v>0.166</v>
+        <v>0.238</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
@@ -1866,22 +1911,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B45">
-        <v>545</v>
+        <v>3633</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="E45">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F45">
-        <v>0.151</v>
+        <v>0.238</v>
       </c>
       <c r="G45" t="s">
         <v>11</v>
@@ -1892,22 +1937,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B46">
-        <v>285</v>
+        <v>465</v>
       </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E46">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F46">
-        <v>0.128</v>
+        <v>0.118</v>
       </c>
       <c r="G46" t="s">
         <v>11</v>
@@ -1921,19 +1966,19 @@
         <v>8</v>
       </c>
       <c r="B47">
-        <v>2064</v>
+        <v>274</v>
       </c>
       <c r="C47" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="E47">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F47">
-        <v>0.127</v>
+        <v>0.107</v>
       </c>
       <c r="G47" t="s">
         <v>11</v>
@@ -1944,22 +1989,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B48">
-        <v>2068</v>
+        <v>3189</v>
       </c>
       <c r="C48" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D48" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E48">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F48">
-        <v>0.127</v>
+        <v>0.117</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
@@ -1970,22 +2015,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B49">
-        <v>3278</v>
+        <v>1124</v>
       </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D49" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E49">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F49">
-        <v>0.118</v>
+        <v>0.195</v>
       </c>
       <c r="G49" t="s">
         <v>11</v>
@@ -1996,22 +2041,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B50">
-        <v>397</v>
+        <v>1125</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D50" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="E50">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F50">
-        <v>0.126</v>
+        <v>0.195</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
@@ -2025,19 +2070,19 @@
         <v>8</v>
       </c>
       <c r="B51">
-        <v>3273</v>
+        <v>286</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D51" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="E51">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F51">
-        <v>0.134</v>
+        <v>0.106</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
@@ -2048,22 +2093,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B52">
-        <v>3279</v>
+        <v>3190</v>
       </c>
       <c r="C52" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="D52" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E52">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F52">
-        <v>0.123</v>
+        <v>0.117</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
@@ -2074,22 +2119,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B53">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="C53" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="D53" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="E53">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F53">
-        <v>0.145</v>
+        <v>0.129</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
@@ -2100,22 +2145,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B54">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C54" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="E54">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F54">
-        <v>0.123</v>
+        <v>0.145</v>
       </c>
       <c r="G54" t="s">
         <v>11</v>
@@ -2129,19 +2174,19 @@
         <v>8</v>
       </c>
       <c r="B55">
-        <v>2110</v>
+        <v>471</v>
       </c>
       <c r="C55" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D55" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E55">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F55">
-        <v>0.131</v>
+        <v>0.116</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
@@ -2152,22 +2197,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B56">
-        <v>580</v>
+        <v>514</v>
       </c>
       <c r="C56" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="D56" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="E56">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F56">
-        <v>0.157</v>
+        <v>0.128</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
@@ -2181,19 +2226,19 @@
         <v>8</v>
       </c>
       <c r="B57">
-        <v>2066</v>
+        <v>472</v>
       </c>
       <c r="C57" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="D57" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E57">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F57">
-        <v>0.12</v>
+        <v>0.144</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
@@ -2204,22 +2249,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B58">
-        <v>2111</v>
+        <v>2063</v>
       </c>
       <c r="C58" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D58" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E58">
         <v>12</v>
       </c>
       <c r="F58">
-        <v>0.129</v>
+        <v>0.096</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -2230,22 +2275,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B59">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C59" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D59" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E59">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F59">
-        <v>0.14</v>
+        <v>0.163</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
@@ -2256,22 +2301,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B60">
-        <v>3177</v>
+        <v>3562</v>
       </c>
       <c r="C60" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D60" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="E60">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F60">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
@@ -2282,22 +2327,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B61">
-        <v>378</v>
+        <v>3563</v>
       </c>
       <c r="C61" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D61" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E61">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F61">
-        <v>0.128</v>
+        <v>0.19</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
@@ -2308,22 +2353,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B62">
-        <v>427</v>
+        <v>2982</v>
       </c>
       <c r="C62" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="E62">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F62">
-        <v>0.128</v>
+        <v>0.114</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
@@ -2334,22 +2379,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B63">
-        <v>330</v>
+        <v>395</v>
       </c>
       <c r="C63" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D63" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E63">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F63">
-        <v>0.118</v>
+        <v>0.142</v>
       </c>
       <c r="G63" t="s">
         <v>11</v>
@@ -2360,22 +2405,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B64">
-        <v>439</v>
+        <v>512</v>
       </c>
       <c r="C64" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D64" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E64">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F64">
-        <v>0.17</v>
+        <v>0.113</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
@@ -2386,22 +2431,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B65">
-        <v>3179</v>
+        <v>3186</v>
       </c>
       <c r="C65" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="E65">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F65">
-        <v>0.153</v>
+        <v>0.125</v>
       </c>
       <c r="G65" t="s">
         <v>11</v>
@@ -2412,22 +2457,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B66">
-        <v>323</v>
+        <v>492</v>
       </c>
       <c r="C66" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D66" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="E66">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F66">
-        <v>0.127</v>
+        <v>0.187</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
@@ -2438,22 +2483,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B67">
-        <v>417</v>
+        <v>3129</v>
       </c>
       <c r="C67" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D67" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E67">
         <v>10</v>
       </c>
       <c r="F67">
-        <v>0.151</v>
+        <v>0.112</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
@@ -2464,22 +2509,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B68">
-        <v>3176</v>
+        <v>3636</v>
       </c>
       <c r="C68" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="D68" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E68">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F68">
-        <v>0.106</v>
+        <v>0.16</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
@@ -2490,22 +2535,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B69">
-        <v>491</v>
+        <v>3637</v>
       </c>
       <c r="C69" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D69" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="E69">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F69">
-        <v>0.148</v>
+        <v>0.16</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -2519,19 +2564,19 @@
         <v>8</v>
       </c>
       <c r="B70">
-        <v>3294</v>
+        <v>530</v>
       </c>
       <c r="C70" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="D70" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="E70">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F70">
-        <v>0.134</v>
+        <v>0.112</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
@@ -2542,22 +2587,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B71">
-        <v>381</v>
+        <v>466</v>
       </c>
       <c r="C71" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D71" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="E71">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F71">
-        <v>0.123</v>
+        <v>0.124</v>
       </c>
       <c r="G71" t="s">
         <v>11</v>
@@ -2568,22 +2613,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B72">
-        <v>403</v>
+        <v>3080</v>
       </c>
       <c r="C72" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D72" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E72">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F72">
-        <v>0.122</v>
+        <v>0.111</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
@@ -2594,22 +2639,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B73">
-        <v>350</v>
+        <v>3081</v>
       </c>
       <c r="C73" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D73" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="E73">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F73">
-        <v>0.098</v>
+        <v>0.111</v>
       </c>
       <c r="G73" t="s">
         <v>11</v>
@@ -2620,22 +2665,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B74">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="C74" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D74" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="E74">
         <v>9</v>
       </c>
       <c r="F74">
-        <v>0.162</v>
+        <v>0.123</v>
       </c>
       <c r="G74" t="s">
         <v>11</v>
@@ -2649,19 +2694,19 @@
         <v>8</v>
       </c>
       <c r="B75">
-        <v>3272</v>
+        <v>451</v>
       </c>
       <c r="C75" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="E75">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F75">
-        <v>0.131</v>
+        <v>0.11</v>
       </c>
       <c r="G75" t="s">
         <v>11</v>
@@ -2672,22 +2717,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B76">
-        <v>376</v>
+        <v>2957</v>
       </c>
       <c r="C76" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D76" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="E76">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F76">
-        <v>0.103</v>
+        <v>0.122</v>
       </c>
       <c r="G76" t="s">
         <v>11</v>
@@ -2698,22 +2743,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B77">
-        <v>375</v>
+        <v>503</v>
       </c>
       <c r="C77" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D77" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="E77">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F77">
-        <v>0.119</v>
+        <v>0.085</v>
       </c>
       <c r="G77" t="s">
         <v>11</v>
@@ -2727,19 +2772,19 @@
         <v>8</v>
       </c>
       <c r="B78">
-        <v>3144</v>
+        <v>399</v>
       </c>
       <c r="C78" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D78" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E78">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F78">
-        <v>0.118</v>
+        <v>0.137</v>
       </c>
       <c r="G78" t="s">
         <v>11</v>
@@ -2750,22 +2795,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B79">
-        <v>3145</v>
+        <v>3634</v>
       </c>
       <c r="C79" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="E79">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F79">
-        <v>0.118</v>
+        <v>0.156</v>
       </c>
       <c r="G79" t="s">
         <v>11</v>
@@ -2776,22 +2821,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B80">
-        <v>3110</v>
+        <v>3635</v>
       </c>
       <c r="C80" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D80" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="E80">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F80">
-        <v>0.128</v>
+        <v>0.156</v>
       </c>
       <c r="G80" t="s">
         <v>11</v>
@@ -2805,19 +2850,19 @@
         <v>8</v>
       </c>
       <c r="B81">
-        <v>3111</v>
+        <v>401</v>
       </c>
       <c r="C81" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D81" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E81">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F81">
-        <v>0.128</v>
+        <v>0.137</v>
       </c>
       <c r="G81" t="s">
         <v>11</v>

--- a/docs/olife-geo/장소_질문_2차.xlsx
+++ b/docs/olife-geo/장소_질문_2차.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="106">
   <si>
     <t>프로그램</t>
   </si>
@@ -37,343 +37,298 @@
     <t>세부 장소 (답, 쉼표로 여러 곳)</t>
   </si>
   <si>
+    <t>세테기</t>
+  </si>
+  <si>
+    <t>중국한시기행9 황허(黃河)2 3-4부</t>
+  </si>
+  <si>
+    <t>중국</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>상상보다 멋진 튀르키예 3부</t>
+  </si>
+  <si>
+    <t>튀르키예</t>
+  </si>
+  <si>
+    <t>중국고사유랑1 3부</t>
+  </si>
+  <si>
+    <t>상상보다 멋진 튀르키예 1-2부</t>
+  </si>
+  <si>
+    <t>상상보다 멋진 튀르키예 3-4부</t>
+  </si>
+  <si>
     <t>걸세</t>
   </si>
   <si>
-    <t>스위스 알프스 - 만년설이 유혹하다</t>
-  </si>
-  <si>
-    <t>스위스</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>스와질란드 - 아프리카의 스위스</t>
-  </si>
-  <si>
-    <t>에스와티니</t>
-  </si>
-  <si>
-    <t>세테기</t>
-  </si>
-  <si>
-    <t>그 여름의 끝, 그리스 섬 기행 4부</t>
+    <t>탄자니아 - 인도양에서 아프리카의 지붕까지</t>
+  </si>
+  <si>
+    <t>탄자니아</t>
+  </si>
+  <si>
+    <t>황금보다 아름다운 골든 트라이앵글 1-2부</t>
+  </si>
+  <si>
+    <t>태국</t>
+  </si>
+  <si>
+    <t>중국한시기행9 황허(黃河)2 1-2부</t>
+  </si>
+  <si>
+    <t>러시아 - 러시아의 붉은 심장</t>
+  </si>
+  <si>
+    <t>러시아</t>
+  </si>
+  <si>
+    <t>베트남 중부 - 따스한 미소가 꽃피다</t>
+  </si>
+  <si>
+    <t>베트남</t>
+  </si>
+  <si>
+    <t>중국 소수민족 음식 기행 1-2부</t>
+  </si>
+  <si>
+    <t>황금보다 아름다운 골든 트라이앵글 3-4부</t>
+  </si>
+  <si>
+    <t>중국고사유랑1 3-4부</t>
+  </si>
+  <si>
+    <t>히말라야의 동물들 네팔에 반하다 1-2부</t>
+  </si>
+  <si>
+    <t>네팔</t>
+  </si>
+  <si>
+    <t>노르웨이 - 빙하가 빚은 대자연, 노르웨이 서부</t>
+  </si>
+  <si>
+    <t>노르웨이</t>
+  </si>
+  <si>
+    <t>남아공 - 지구의 끝</t>
+  </si>
+  <si>
+    <t>남아프리카공화국</t>
+  </si>
+  <si>
+    <t>중국고사유랑1 1-2부</t>
+  </si>
+  <si>
+    <t>네팔 - 열대림을 품은 히말라야의 나라</t>
+  </si>
+  <si>
+    <t>자연에 묻힌 앙코르의 전설 - 캄보디아 씨엠립</t>
+  </si>
+  <si>
+    <t>캄보디아</t>
+  </si>
+  <si>
+    <t>과테말라 - 마야의 중심</t>
+  </si>
+  <si>
+    <t>과테말라</t>
+  </si>
+  <si>
+    <t>아프리카 버킷리스트,탄자니아 3-4부</t>
+  </si>
+  <si>
+    <t>실크로드 재발견 튀르키예 3-4부</t>
+  </si>
+  <si>
+    <t>천국 위에 태국 3-4부</t>
+  </si>
+  <si>
+    <t>중국 소수민족 음식 기행 4부</t>
+  </si>
+  <si>
+    <t>지치고 힘들 때 노르웨이 3-4부</t>
+  </si>
+  <si>
+    <t>지치고 힘들 때 노르웨이 1-2부</t>
+  </si>
+  <si>
+    <t>기다렸다, 그 맛! 타이완 3-4부</t>
+  </si>
+  <si>
+    <t>타이완</t>
+  </si>
+  <si>
+    <t>한번쯤은, 하염없이 몽골 1-3부</t>
+  </si>
+  <si>
+    <t>몽골</t>
+  </si>
+  <si>
+    <t>중국 소수민족 음식 기행 3부</t>
+  </si>
+  <si>
+    <t>미얀마 - 미얀마 기차여행</t>
+  </si>
+  <si>
+    <t>미얀마</t>
+  </si>
+  <si>
+    <t>그 섬에 가면 인도네시아 3-4부</t>
+  </si>
+  <si>
+    <t>인도네시아</t>
+  </si>
+  <si>
+    <t>아랍에미리트 아부다비 - 중동의 문화수도를 꿈꾼다</t>
+  </si>
+  <si>
+    <t>아랍에미리트</t>
+  </si>
+  <si>
+    <t>하늘이 주는 선물 오로라, 캐나다</t>
+  </si>
+  <si>
+    <t>캐나다</t>
+  </si>
+  <si>
+    <t>태양과 가장 가까운 곳, 적도의 안데스 - 에콰도르</t>
+  </si>
+  <si>
+    <t>에콰도르</t>
+  </si>
+  <si>
+    <t>신이 만든 놀이터, 노르웨이 3-4부</t>
+  </si>
+  <si>
+    <t>라트비아 - 수줍은 미소의 나라</t>
+  </si>
+  <si>
+    <t>라트비아</t>
+  </si>
+  <si>
+    <t>천국 위에 태국 1-2부</t>
+  </si>
+  <si>
+    <t>몰도바 - 작지만 강한 나라, 몰도바</t>
+  </si>
+  <si>
+    <t>몰도바</t>
+  </si>
+  <si>
+    <t>이탈리아 알토 아디제 - 티롤 왕국을 찾아서</t>
+  </si>
+  <si>
+    <t>이탈리아, 오스트리아</t>
+  </si>
+  <si>
+    <t>그 여름의 끝, 그리스 섬 기행 1부</t>
   </si>
   <si>
     <t>그리스</t>
   </si>
   <si>
-    <t>차이 나는 중국 기행 3-4부</t>
-  </si>
-  <si>
-    <t>중국</t>
-  </si>
-  <si>
-    <t>알프스 따라 스위스 1-2부</t>
-  </si>
-  <si>
-    <t>실크로드 재발견 튀르키예 1-2부</t>
-  </si>
-  <si>
-    <t>튀르키예</t>
-  </si>
-  <si>
-    <t>그 여름의 끝, 그리스 섬 기행 3부</t>
-  </si>
-  <si>
-    <t>태평양의 행복한 메아리 - 마셜제도</t>
-  </si>
-  <si>
-    <t>북한</t>
-  </si>
-  <si>
-    <t>정다운 아시아 4부-신비한 필리핀</t>
-  </si>
-  <si>
-    <t>필리핀</t>
-  </si>
-  <si>
-    <t>멕시코 칸쿤 - 카브리해 천국의 문</t>
+    <t>풍요의 아프리카, 나미비아</t>
+  </si>
+  <si>
+    <t>나미비아</t>
+  </si>
+  <si>
+    <t>그 여름의 끝, 그리스 섬 기행 2부</t>
+  </si>
+  <si>
+    <t>스웨덴 - 스웨덴의 가을 속으로</t>
+  </si>
+  <si>
+    <t>스웨덴</t>
+  </si>
+  <si>
+    <t>기다렸다, 그 맛! 타이완 1-2부</t>
+  </si>
+  <si>
+    <t>뉴질랜드 남섬 - 순수 자연이 유혹하다</t>
+  </si>
+  <si>
+    <t>뉴질랜드</t>
+  </si>
+  <si>
+    <t>베트남 하이퐁 - 왕이 사랑한 바다</t>
+  </si>
+  <si>
+    <t>미지의 섬나라 - 마다가스카르), 396(불가리아-산, 장비, 수도원 그리고 불가리아</t>
+  </si>
+  <si>
+    <t>불가리아</t>
+  </si>
+  <si>
+    <t>벨기에 - 모자이크로 멋진 화음을</t>
+  </si>
+  <si>
+    <t>벨기에</t>
+  </si>
+  <si>
+    <t>구름이 빚은 무지개 나라 - 겨울 아일랜드</t>
+  </si>
+  <si>
+    <t>아일랜드</t>
+  </si>
+  <si>
+    <t>코스타리카 - 화산, 커피 그리고 뿌라비다</t>
+  </si>
+  <si>
+    <t>코스타리카</t>
+  </si>
+  <si>
+    <t>키르기스스탄 - 중앙아시아의 후른 섬</t>
+  </si>
+  <si>
+    <t>키르기스스탄</t>
+  </si>
+  <si>
+    <t>중국 - 지린성, 겨울왕국을 가다</t>
+  </si>
+  <si>
+    <t>포르투갈 - 어제의 바다를 걷다</t>
+  </si>
+  <si>
+    <t>포르투갈</t>
+  </si>
+  <si>
+    <t>동양의 에메랄드 - 말레이시아 페낭</t>
+  </si>
+  <si>
+    <t>말레이시아</t>
+  </si>
+  <si>
+    <t>잉글랜드의 녹색 심장 - 요크셔·레이크 디스크릭트</t>
+  </si>
+  <si>
+    <t>영국</t>
+  </si>
+  <si>
+    <t>멕시코 유카탄 - 삶은 계속된다</t>
   </si>
   <si>
     <t>멕시코</t>
   </si>
   <si>
-    <t>히말라야의 동물들 네팔에 반하다 3-4부</t>
-  </si>
-  <si>
-    <t>네팔</t>
-  </si>
-  <si>
-    <t>파키스탄 - 향기로운 땅</t>
-  </si>
-  <si>
-    <t>파키스탄</t>
-  </si>
-  <si>
-    <t>알프스 따라 스위스 3-4부</t>
-  </si>
-  <si>
-    <t>정다운 아시아 1부 -행복한 부탄</t>
-  </si>
-  <si>
-    <t>부탄</t>
-  </si>
-  <si>
-    <t>영국 - 영국의 정원, 켄트</t>
-  </si>
-  <si>
-    <t>영국</t>
-  </si>
-  <si>
-    <t>동유럽 리버크루즈), 397(라트비아-수줍은 미소의 나라</t>
-  </si>
-  <si>
-    <t>라트비아</t>
-  </si>
-  <si>
-    <t>일본 - 가을 향기 속 설렘을 찾아</t>
-  </si>
-  <si>
-    <t>일본</t>
-  </si>
-  <si>
-    <t>UHD특집 1부 - 아이슬란드</t>
-  </si>
-  <si>
-    <t>아이슬란드</t>
-  </si>
-  <si>
-    <t>방글라데시 - 소박한 꿈과 미소의 나라</t>
-  </si>
-  <si>
-    <t>방글라데시</t>
-  </si>
-  <si>
-    <t>황금빛 도시에서 순수를 만나다 - 미얀마</t>
-  </si>
-  <si>
-    <t>미얀마</t>
-  </si>
-  <si>
-    <t>로맨틱 홀리데이, 체코 1-2부</t>
-  </si>
-  <si>
-    <t>체코</t>
-  </si>
-  <si>
-    <t>인도 - 언덕의 여왕, 만년설이 유혹하다</t>
-  </si>
-  <si>
-    <t>인도</t>
-  </si>
-  <si>
-    <t>내 인생의 피에스타 콜롬비아 4부</t>
-  </si>
-  <si>
-    <t>콜롬비아</t>
-  </si>
-  <si>
-    <t>마음이 평화로운 나라 - 브루나이</t>
-  </si>
-  <si>
-    <t>브루나이</t>
-  </si>
-  <si>
-    <t>싱가포르 - 도시를 걷다</t>
-  </si>
-  <si>
-    <t>싱가포르</t>
-  </si>
-  <si>
-    <t>일본 - 규슈 올레를 걷다</t>
-  </si>
-  <si>
-    <t>불가리아 - 산, 장비, 수도원 그리고 불가리아</t>
-  </si>
-  <si>
-    <t>불가리아</t>
-  </si>
-  <si>
-    <t>그 섬에 가면 인도네시아 1-2부</t>
-  </si>
-  <si>
-    <t>인도네시아</t>
-  </si>
-  <si>
-    <t>한번쯤은, 하염없이 몽골 1-3부</t>
-  </si>
-  <si>
-    <t>몽골</t>
-  </si>
-  <si>
-    <t>그리스 로도스 - 태양과 함께 빛나다</t>
-  </si>
-  <si>
-    <t>정다운 아시아 3부-궁금한 라오스</t>
-  </si>
-  <si>
-    <t>라오스</t>
-  </si>
-  <si>
-    <t>알수록 놀라운, 베트남 남부 3-4부</t>
-  </si>
-  <si>
-    <t>베트남</t>
-  </si>
-  <si>
-    <t>페루 푸노 - 하늘길을 걷다</t>
-  </si>
-  <si>
-    <t>페루</t>
-  </si>
-  <si>
-    <t>인도 - 다채로운 빛깔의 여유</t>
-  </si>
-  <si>
-    <t>미국 - 미국 서부의 품격, 센트럴 코스트</t>
-  </si>
-  <si>
-    <t>미국</t>
-  </si>
-  <si>
-    <t>중국 명산 기행 3-4부</t>
-  </si>
-  <si>
-    <t>모로코 - 문화의 용광로</t>
-  </si>
-  <si>
-    <t>모로코</t>
-  </si>
-  <si>
-    <t>남미의 심장 - 파라과이</t>
-  </si>
-  <si>
-    <t>파라과이</t>
-  </si>
-  <si>
-    <t>내 인생의 피에스타 콜롬비아 2부</t>
-  </si>
-  <si>
-    <t>중국한시기행4-한시와 떠나는 실크로드 1-2부</t>
-  </si>
-  <si>
-    <t>대서양에 부는 뜨거운 바람 - 브라질</t>
-  </si>
-  <si>
-    <t>브라질</t>
-  </si>
-  <si>
-    <t>내 인생의 피에스타 콜롬비아 3부</t>
-  </si>
-  <si>
-    <t>캐나다 - 캐나다의 새로운 느낌, 유콘</t>
-  </si>
-  <si>
-    <t>캐나다</t>
-  </si>
-  <si>
-    <t>조지아 - 기어이 지켜낸 땅</t>
-  </si>
-  <si>
-    <t>조지아</t>
-  </si>
-  <si>
-    <t>도미니카-카리브 해의 중심, 도미니카), 465(모로코-문화의 용광로</t>
-  </si>
-  <si>
-    <t>아르헨티나 파타고니아 - 바람이 품은 아름다움</t>
-  </si>
-  <si>
-    <t>아르헨티나</t>
-  </si>
-  <si>
-    <t>중국 - 삶은 노래가 되고</t>
-  </si>
-  <si>
-    <t>콜롬비아 메데인 - 인데스의 두 얼굴</t>
-  </si>
-  <si>
-    <t>중국 남부 핫 플레이스 1-2부</t>
-  </si>
-  <si>
-    <t>정다운 아시아 2부-캄보디아</t>
-  </si>
-  <si>
-    <t>캄보디아</t>
-  </si>
-  <si>
-    <t>아일랜드 - 문학과 열정의 나라</t>
-  </si>
-  <si>
-    <t>아일랜드</t>
-  </si>
-  <si>
-    <t>이집트 - 파라오의 땅, 신화를 만나다</t>
-  </si>
-  <si>
-    <t>이집트</t>
-  </si>
-  <si>
-    <t>자연이 그리워서,동말레이시아 3-4부</t>
-  </si>
-  <si>
-    <t>말레이시아</t>
-  </si>
-  <si>
-    <t>짐바브웨 - 위대한 야생의 나라</t>
-  </si>
-  <si>
-    <t>짐바브웨</t>
-  </si>
-  <si>
-    <t>보고 싶었다,크로아티아 1-2부</t>
-  </si>
-  <si>
-    <t>크로아티아</t>
-  </si>
-  <si>
-    <t>베트남 육향만리 3-4부</t>
-  </si>
-  <si>
-    <t>미국 서부</t>
-  </si>
-  <si>
-    <t>인도네시아 - 고대 문명의 나라, 인도네시아</t>
-  </si>
-  <si>
-    <t>열정이 그리워서, 스페인 1-2부</t>
-  </si>
-  <si>
-    <t>스페인</t>
-  </si>
-  <si>
-    <t>태국 끄라비, 뜨랑 - 신비와 모험의 땅</t>
-  </si>
-  <si>
-    <t>태국</t>
-  </si>
-  <si>
-    <t>러시아 블라디보스토크 - 아시아의 러시아</t>
-  </si>
-  <si>
-    <t>러시아</t>
-  </si>
-  <si>
-    <t>차이 나는 중국 기행 1-2부</t>
-  </si>
-  <si>
-    <t>남태평양 사모아</t>
-  </si>
-  <si>
-    <t>스페인 안달루시아 - 이슬람 문명의 흔적</t>
-  </si>
-  <si>
-    <t>베트남 육향만리 1-2부</t>
-  </si>
-  <si>
-    <t>아르헨티나 - 전설 속 행운을 만나다</t>
+    <t>우간다 - 원색의 자연 속으로</t>
+  </si>
+  <si>
+    <t>우간다</t>
+  </si>
+  <si>
+    <t>아프리카 버킷리스트,탄자니아 1-2부</t>
+  </si>
+  <si>
+    <t>칠레에서 세계 일주 3-4부</t>
+  </si>
+  <si>
+    <t>칠레</t>
   </si>
 </sst>
 </file>
@@ -796,7 +751,7 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>407</v>
+        <v>2093</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -805,10 +760,10 @@
         <v>10</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0.139</v>
+        <v>0.175</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -822,7 +777,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>372</v>
+        <v>2028</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -831,10 +786,10 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>0.116</v>
+        <v>0.142</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -845,22 +800,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>3298</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="B4">
-        <v>2113</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>0.139</v>
+        <v>0.117</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -871,22 +826,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>2959</v>
+        <v>2027</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F5">
-        <v>0.154</v>
+        <v>0.13</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -897,22 +852,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>3260</v>
+        <v>2029</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>0.138</v>
+        <v>0.147</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -923,22 +878,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7">
-        <v>3261</v>
+        <v>404</v>
       </c>
       <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
       <c r="E7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>0.138</v>
+        <v>0.167</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -949,22 +904,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>3293</v>
+        <v>2026</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>0.125</v>
+        <v>0.124</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -975,22 +930,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>2112</v>
+        <v>2075</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9">
         <v>16</v>
       </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
       <c r="F9">
-        <v>0.137</v>
+        <v>0.132</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
@@ -1004,19 +959,19 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>332</v>
+        <v>2091</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>0.124</v>
+        <v>0.161</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -1027,22 +982,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B11">
-        <v>2984</v>
+        <v>446</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>0.151</v>
+        <v>0.161</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -1053,22 +1008,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B12">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>0.123</v>
+        <v>0.139</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -1079,22 +1034,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13">
+        <v>2058</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13">
         <v>14</v>
       </c>
-      <c r="B13">
-        <v>2024</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13">
-        <v>12</v>
-      </c>
       <c r="F13">
-        <v>0.113</v>
+        <v>0.149</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -1105,22 +1060,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14">
+        <v>2059</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14">
         <v>14</v>
       </c>
-      <c r="B14">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14">
-        <v>12</v>
-      </c>
       <c r="F14">
-        <v>0.113</v>
+        <v>0.148</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -1134,19 +1089,19 @@
         <v>8</v>
       </c>
       <c r="B15">
-        <v>526</v>
+        <v>2074</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>0.169</v>
+        <v>0.129</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -1157,22 +1112,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B16">
-        <v>3262</v>
+        <v>2077</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E16">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F16">
-        <v>0.147</v>
+        <v>0.136</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1183,22 +1138,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B17">
-        <v>3292</v>
+        <v>2076</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
         <v>21</v>
       </c>
       <c r="E17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F17">
-        <v>0.12</v>
+        <v>0.136</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -1209,22 +1164,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B18">
-        <v>2981</v>
+        <v>2092</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F18">
-        <v>0.132</v>
+        <v>0.156</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -1238,19 +1193,19 @@
         <v>8</v>
       </c>
       <c r="B19">
-        <v>414</v>
+        <v>3299</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F19">
-        <v>0.146</v>
+        <v>0.119</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -1264,19 +1219,19 @@
         <v>8</v>
       </c>
       <c r="B20">
-        <v>532</v>
+        <v>2090</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E20">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F20">
-        <v>0.119</v>
+        <v>0.155</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
@@ -1290,19 +1245,19 @@
         <v>8</v>
       </c>
       <c r="B21">
-        <v>410</v>
+        <v>2023</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F21">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
@@ -1316,19 +1271,19 @@
         <v>8</v>
       </c>
       <c r="B22">
-        <v>531</v>
+        <v>2022</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E22">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F22">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="G22" t="s">
         <v>11</v>
@@ -1339,22 +1294,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B23">
-        <v>522</v>
+        <v>455</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F23">
-        <v>0.13</v>
+        <v>0.173</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
@@ -1365,22 +1320,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B24">
-        <v>302</v>
+        <v>380</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F24">
-        <v>0.118</v>
+        <v>0.145</v>
       </c>
       <c r="G24" t="s">
         <v>11</v>
@@ -1391,22 +1346,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B25">
-        <v>2958</v>
+        <v>3296</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F25">
-        <v>0.144</v>
+        <v>0.099</v>
       </c>
       <c r="G25" t="s">
         <v>11</v>
@@ -1417,22 +1372,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B26">
-        <v>3156</v>
+        <v>379</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E26">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F26">
-        <v>0.117</v>
+        <v>0.124</v>
       </c>
       <c r="G26" t="s">
         <v>11</v>
@@ -1443,22 +1398,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B27">
-        <v>3157</v>
+        <v>3297</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F27">
-        <v>0.117</v>
+        <v>0.102</v>
       </c>
       <c r="G27" t="s">
         <v>11</v>
@@ -1469,22 +1424,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B28">
-        <v>413</v>
+        <v>284</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F28">
-        <v>0.126</v>
+        <v>0.14</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
@@ -1495,22 +1450,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B29">
-        <v>3191</v>
+        <v>367</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F29">
-        <v>0.126</v>
+        <v>0.12</v>
       </c>
       <c r="G29" t="s">
         <v>11</v>
@@ -1524,19 +1479,19 @@
         <v>8</v>
       </c>
       <c r="B30">
-        <v>358</v>
+        <v>3147</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F30">
-        <v>0.114</v>
+        <v>0.148</v>
       </c>
       <c r="G30" t="s">
         <v>11</v>
@@ -1550,19 +1505,19 @@
         <v>8</v>
       </c>
       <c r="B31">
-        <v>394</v>
+        <v>3295</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31">
-        <v>0.104</v>
+        <v>0.161</v>
       </c>
       <c r="G31" t="s">
         <v>11</v>
@@ -1576,19 +1531,19 @@
         <v>8</v>
       </c>
       <c r="B32">
-        <v>459</v>
+        <v>3275</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E32">
         <v>10</v>
       </c>
       <c r="F32">
-        <v>0.124</v>
+        <v>0.177</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
@@ -1602,19 +1557,19 @@
         <v>8</v>
       </c>
       <c r="B33">
-        <v>396</v>
+        <v>2061</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E33">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F33">
-        <v>0.113</v>
+        <v>0.135</v>
       </c>
       <c r="G33" t="s">
         <v>11</v>
@@ -1625,22 +1580,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B34">
-        <v>2062</v>
+        <v>3146</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D34" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="E34">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F34">
-        <v>0.095</v>
+        <v>0.144</v>
       </c>
       <c r="G34" t="s">
         <v>11</v>
@@ -1651,22 +1606,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B35">
-        <v>2390</v>
+        <v>2069</v>
       </c>
       <c r="C35" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="E35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F35">
-        <v>0.112</v>
+        <v>0.132</v>
       </c>
       <c r="G35" t="s">
         <v>11</v>
@@ -1680,19 +1635,19 @@
         <v>8</v>
       </c>
       <c r="B36">
-        <v>419</v>
+        <v>2067</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E36">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F36">
-        <v>0.103</v>
+        <v>0.131</v>
       </c>
       <c r="G36" t="s">
         <v>11</v>
@@ -1703,19 +1658,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B37">
-        <v>2983</v>
+        <v>3178</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D37" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F37">
         <v>0.154</v>
@@ -1729,22 +1684,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B38">
-        <v>3151</v>
+        <v>2388</v>
       </c>
       <c r="C38" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E38">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F38">
-        <v>0.122</v>
+        <v>0.13</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -1755,22 +1710,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B39">
-        <v>3263</v>
+        <v>2389</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="E39">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F39">
-        <v>0.135</v>
+        <v>0.13</v>
       </c>
       <c r="G39" t="s">
         <v>11</v>
@@ -1784,19 +1739,19 @@
         <v>8</v>
       </c>
       <c r="B40">
-        <v>425</v>
+        <v>2060</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="E40">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F40">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -1807,22 +1762,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B41">
-        <v>370</v>
+        <v>484</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D41" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E41">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F41">
-        <v>0.109</v>
+        <v>0.168</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -1836,19 +1791,19 @@
         <v>8</v>
       </c>
       <c r="B42">
-        <v>470</v>
+        <v>2065</v>
       </c>
       <c r="C42" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D42" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E42">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F42">
-        <v>0.109</v>
+        <v>0.128</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -1859,22 +1814,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B43">
-        <v>3150</v>
+        <v>421</v>
       </c>
       <c r="C43" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D43" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E43">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F43">
-        <v>0.119</v>
+        <v>0.151</v>
       </c>
       <c r="G43" t="s">
         <v>11</v>
@@ -1885,22 +1840,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B44">
-        <v>3632</v>
+        <v>3274</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F44">
-        <v>0.238</v>
+        <v>0.166</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
@@ -1911,22 +1866,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B45">
-        <v>3633</v>
+        <v>545</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F45">
-        <v>0.238</v>
+        <v>0.151</v>
       </c>
       <c r="G45" t="s">
         <v>11</v>
@@ -1937,22 +1892,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B46">
-        <v>465</v>
+        <v>285</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D46" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E46">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F46">
-        <v>0.118</v>
+        <v>0.128</v>
       </c>
       <c r="G46" t="s">
         <v>11</v>
@@ -1966,19 +1921,19 @@
         <v>8</v>
       </c>
       <c r="B47">
-        <v>274</v>
+        <v>2064</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="D47" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="E47">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F47">
-        <v>0.107</v>
+        <v>0.127</v>
       </c>
       <c r="G47" t="s">
         <v>11</v>
@@ -1989,22 +1944,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B48">
-        <v>3189</v>
+        <v>2068</v>
       </c>
       <c r="C48" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="D48" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="E48">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F48">
-        <v>0.117</v>
+        <v>0.127</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
@@ -2015,22 +1970,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49">
+        <v>3278</v>
+      </c>
+      <c r="C49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D49" t="s">
+        <v>33</v>
+      </c>
+      <c r="E49">
         <v>14</v>
       </c>
-      <c r="B49">
-        <v>1124</v>
-      </c>
-      <c r="C49" t="s">
-        <v>81</v>
-      </c>
-      <c r="D49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49">
-        <v>6</v>
-      </c>
       <c r="F49">
-        <v>0.195</v>
+        <v>0.118</v>
       </c>
       <c r="G49" t="s">
         <v>11</v>
@@ -2041,22 +1996,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B50">
-        <v>1125</v>
+        <v>397</v>
       </c>
       <c r="C50" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="D50" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="E50">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F50">
-        <v>0.195</v>
+        <v>0.126</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
@@ -2070,19 +2025,19 @@
         <v>8</v>
       </c>
       <c r="B51">
-        <v>286</v>
+        <v>3273</v>
       </c>
       <c r="C51" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F51">
-        <v>0.106</v>
+        <v>0.134</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
@@ -2093,22 +2048,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B52">
-        <v>3190</v>
+        <v>3279</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="D52" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="E52">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F52">
-        <v>0.117</v>
+        <v>0.123</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
@@ -2119,22 +2074,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B53">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C53" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D53" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E53">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F53">
-        <v>0.129</v>
+        <v>0.145</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
@@ -2145,22 +2100,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B54">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C54" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D54" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="E54">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F54">
-        <v>0.145</v>
+        <v>0.123</v>
       </c>
       <c r="G54" t="s">
         <v>11</v>
@@ -2174,19 +2129,19 @@
         <v>8</v>
       </c>
       <c r="B55">
-        <v>471</v>
+        <v>2110</v>
       </c>
       <c r="C55" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D55" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E55">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F55">
-        <v>0.116</v>
+        <v>0.131</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
@@ -2197,22 +2152,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B56">
-        <v>514</v>
+        <v>580</v>
       </c>
       <c r="C56" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="D56" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E56">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F56">
-        <v>0.128</v>
+        <v>0.157</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
@@ -2226,19 +2181,19 @@
         <v>8</v>
       </c>
       <c r="B57">
-        <v>472</v>
+        <v>2066</v>
       </c>
       <c r="C57" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="D57" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E57">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F57">
-        <v>0.144</v>
+        <v>0.12</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
@@ -2249,22 +2204,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B58">
-        <v>2063</v>
+        <v>2111</v>
       </c>
       <c r="C58" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D58" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E58">
         <v>12</v>
       </c>
       <c r="F58">
-        <v>0.096</v>
+        <v>0.129</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -2275,22 +2230,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B59">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C59" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="D59" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="E59">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F59">
-        <v>0.163</v>
+        <v>0.14</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
@@ -2301,22 +2256,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60">
+        <v>3177</v>
+      </c>
+      <c r="C60" t="s">
+        <v>78</v>
+      </c>
+      <c r="D60" t="s">
+        <v>49</v>
+      </c>
+      <c r="E60">
         <v>14</v>
       </c>
-      <c r="B60">
-        <v>3562</v>
-      </c>
-      <c r="C60" t="s">
-        <v>94</v>
-      </c>
-      <c r="D60" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60">
-        <v>6</v>
-      </c>
       <c r="F60">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
@@ -2327,22 +2282,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B61">
-        <v>3563</v>
+        <v>378</v>
       </c>
       <c r="C61" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D61" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E61">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F61">
-        <v>0.19</v>
+        <v>0.128</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
@@ -2353,22 +2308,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B62">
-        <v>2982</v>
+        <v>427</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D62" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="E62">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F62">
-        <v>0.114</v>
+        <v>0.128</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
@@ -2379,22 +2334,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B63">
-        <v>395</v>
+        <v>330</v>
       </c>
       <c r="C63" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D63" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E63">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F63">
-        <v>0.142</v>
+        <v>0.118</v>
       </c>
       <c r="G63" t="s">
         <v>11</v>
@@ -2405,22 +2360,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B64">
-        <v>512</v>
+        <v>439</v>
       </c>
       <c r="C64" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D64" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E64">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F64">
-        <v>0.113</v>
+        <v>0.17</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
@@ -2431,22 +2386,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B65">
-        <v>3186</v>
+        <v>3179</v>
       </c>
       <c r="C65" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="D65" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="E65">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F65">
-        <v>0.125</v>
+        <v>0.153</v>
       </c>
       <c r="G65" t="s">
         <v>11</v>
@@ -2457,22 +2412,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B66">
-        <v>492</v>
+        <v>323</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D66" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E66">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F66">
-        <v>0.187</v>
+        <v>0.127</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
@@ -2483,22 +2438,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B67">
-        <v>3129</v>
+        <v>417</v>
       </c>
       <c r="C67" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D67" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="E67">
         <v>10</v>
       </c>
       <c r="F67">
-        <v>0.112</v>
+        <v>0.151</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
@@ -2509,22 +2464,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68">
+        <v>3176</v>
+      </c>
+      <c r="C68" t="s">
+        <v>78</v>
+      </c>
+      <c r="D68" t="s">
+        <v>49</v>
+      </c>
+      <c r="E68">
         <v>14</v>
       </c>
-      <c r="B68">
-        <v>3636</v>
-      </c>
-      <c r="C68" t="s">
-        <v>107</v>
-      </c>
-      <c r="D68" t="s">
-        <v>69</v>
-      </c>
-      <c r="E68">
-        <v>7</v>
-      </c>
       <c r="F68">
-        <v>0.16</v>
+        <v>0.106</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
@@ -2535,22 +2490,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B69">
-        <v>3637</v>
+        <v>491</v>
       </c>
       <c r="C69" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D69" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E69">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F69">
-        <v>0.16</v>
+        <v>0.148</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -2564,19 +2519,19 @@
         <v>8</v>
       </c>
       <c r="B70">
-        <v>530</v>
+        <v>3294</v>
       </c>
       <c r="C70" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="D70" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="E70">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F70">
-        <v>0.112</v>
+        <v>0.134</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
@@ -2587,22 +2542,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B71">
-        <v>466</v>
+        <v>381</v>
       </c>
       <c r="C71" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="D71" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="E71">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F71">
-        <v>0.124</v>
+        <v>0.123</v>
       </c>
       <c r="G71" t="s">
         <v>11</v>
@@ -2613,22 +2568,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B72">
-        <v>3080</v>
+        <v>403</v>
       </c>
       <c r="C72" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D72" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="E72">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F72">
-        <v>0.111</v>
+        <v>0.122</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
@@ -2639,22 +2594,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B73">
-        <v>3081</v>
+        <v>350</v>
       </c>
       <c r="C73" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D73" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E73">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F73">
-        <v>0.111</v>
+        <v>0.098</v>
       </c>
       <c r="G73" t="s">
         <v>11</v>
@@ -2665,22 +2620,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B74">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="E74">
         <v>9</v>
       </c>
       <c r="F74">
-        <v>0.123</v>
+        <v>0.162</v>
       </c>
       <c r="G74" t="s">
         <v>11</v>
@@ -2694,19 +2649,19 @@
         <v>8</v>
       </c>
       <c r="B75">
-        <v>451</v>
+        <v>3272</v>
       </c>
       <c r="C75" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="D75" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="E75">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F75">
-        <v>0.11</v>
+        <v>0.131</v>
       </c>
       <c r="G75" t="s">
         <v>11</v>
@@ -2717,22 +2672,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>17</v>
+      </c>
+      <c r="B76">
+        <v>376</v>
+      </c>
+      <c r="C76" t="s">
+        <v>99</v>
+      </c>
+      <c r="D76" t="s">
+        <v>100</v>
+      </c>
+      <c r="E76">
         <v>14</v>
       </c>
-      <c r="B76">
-        <v>2957</v>
-      </c>
-      <c r="C76" t="s">
-        <v>116</v>
-      </c>
-      <c r="D76" t="s">
-        <v>18</v>
-      </c>
-      <c r="E76">
-        <v>9</v>
-      </c>
       <c r="F76">
-        <v>0.122</v>
+        <v>0.103</v>
       </c>
       <c r="G76" t="s">
         <v>11</v>
@@ -2743,22 +2698,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B77">
-        <v>503</v>
+        <v>375</v>
       </c>
       <c r="C77" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="D77" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="E77">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F77">
-        <v>0.085</v>
+        <v>0.119</v>
       </c>
       <c r="G77" t="s">
         <v>11</v>
@@ -2772,19 +2727,19 @@
         <v>8</v>
       </c>
       <c r="B78">
-        <v>399</v>
+        <v>3144</v>
       </c>
       <c r="C78" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D78" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="E78">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F78">
-        <v>0.137</v>
+        <v>0.118</v>
       </c>
       <c r="G78" t="s">
         <v>11</v>
@@ -2795,22 +2750,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B79">
-        <v>3634</v>
+        <v>3145</v>
       </c>
       <c r="C79" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="D79" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="E79">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F79">
-        <v>0.156</v>
+        <v>0.118</v>
       </c>
       <c r="G79" t="s">
         <v>11</v>
@@ -2821,22 +2776,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B80">
-        <v>3635</v>
+        <v>3110</v>
       </c>
       <c r="C80" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D80" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="E80">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F80">
-        <v>0.156</v>
+        <v>0.128</v>
       </c>
       <c r="G80" t="s">
         <v>11</v>
@@ -2850,19 +2805,19 @@
         <v>8</v>
       </c>
       <c r="B81">
-        <v>401</v>
+        <v>3111</v>
       </c>
       <c r="C81" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="D81" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="E81">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F81">
-        <v>0.137</v>
+        <v>0.128</v>
       </c>
       <c r="G81" t="s">
         <v>11</v>
